--- a/data/obx_xlsx/NRC.OL.xlsx
+++ b/data/obx_xlsx/NRC.OL.xlsx
@@ -11675,14 +11675,38 @@
       <c r="O58" s="18">
         <v>98.91</v>
       </c>
-      <c r="P58" s="15"/>
-      <c r="Q58" s="15"/>
-      <c r="R58" s="15"/>
-      <c r="S58" s="15"/>
-      <c r="T58" s="15"/>
-      <c r="U58" s="15"/>
-      <c r="V58" s="15"/>
-      <c r="W58" s="15"/>
+      <c r="P58" s="15">
+        <f t="shared" ref="P58:Q58" si="1">SUM(P62)</f>
+        <v>155.69</v>
+      </c>
+      <c r="Q58" s="15">
+        <f t="shared" si="1"/>
+        <v>110.93</v>
+      </c>
+      <c r="R58" s="15">
+        <f t="shared" ref="R58:S58" si="2">SUM(R59:R63,R57)</f>
+        <v>295.81</v>
+      </c>
+      <c r="S58" s="15">
+        <f t="shared" si="2"/>
+        <v>315.84</v>
+      </c>
+      <c r="T58" s="15">
+        <f t="shared" ref="T58:V58" si="3">SUM(T59:T62)</f>
+        <v>265.88</v>
+      </c>
+      <c r="U58" s="15">
+        <f t="shared" si="3"/>
+        <v>315.9</v>
+      </c>
+      <c r="V58" s="15">
+        <f t="shared" si="3"/>
+        <v>103.47</v>
+      </c>
+      <c r="W58" s="15">
+        <f>SUM(W57,W63)</f>
+        <v>19.92</v>
+      </c>
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="13" t="s">
